--- a/data/exports/RdentQAMaster_VersionFQC_updated.xlsx
+++ b/data/exports/RdentQAMaster_VersionFQC_updated.xlsx
@@ -307,7 +307,7 @@
     <t>Does R-dent offer digital partial dentures?</t>
   </si>
   <si>
-    <t>Yes, including 3D Printed Digital Acrylic and FP3D Flexible partials. Digital partials take 5 days. Digital removable cases require 2 extra days for model printing.</t>
+    <t>Yes, including 3D Printed Digital Acrylic and FP3D Flexible partials. Digital partials take 5 days.</t>
   </si>
   <si>
     <t>Does R-dent offer e.max restorations?</t>
